--- a/workspace/sheets/supplier_master.xlsx
+++ b/workspace/sheets/supplier_master.xlsx
@@ -431,12 +431,12 @@
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,17 +494,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shenzhen Parts Co., Ltd.</t>
+          <t>Pearl River Growth Fund II LP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>深圳市零件有限公司</t>
+          <t>珠江成长基金二期</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>shenzhenparts.com</t>
+          <t>prgfund.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>60 days</t>
+          <t>14 days</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>docs/contracts/S01_supply_agreement_2026.pdf</t>
+          <t>docs/contracts/S01_subscription_agreement_2024.pdf</t>
         </is>
       </c>
     </row>
@@ -541,27 +541,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dongguan Precision Electronics Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>东莞精密电子有限公司</t>
-        </is>
-      </c>
+          <t>Harbourview Capital Partners III LP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dg-precision.cn</t>
+          <t>harbourviewcap.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Greater Bay Trust Bank, Dongguan Branch (SWIFT GBTBCNDGXXX)</t>
+          <t>Atlantic Mercantile Bank, New York (SWIFT ATMBUS33)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7800 1123 4588 0062</t>
+          <t>8841-2207-5530</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -571,12 +567,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>10 days</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>docs/contracts/S02_supply_agreement_2026.pdf</t>
+          <t>docs/contracts/S02_side_letter_2024.pdf</t>
         </is>
       </c>
     </row>
@@ -588,13 +584,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pacific Freight Logistics Ltd</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Peak Estates Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>峰譽物業管理有限公司</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pacfreight.com.hk</t>
+          <t>peakestates.com.hk</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>docs/contracts/S03_freight_rate_card_2026.pdf</t>
+          <t>docs/contracts/S03_property_management_agreement_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -631,17 +631,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kowloon Bay Properties Ltd</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>九龍灣置業有限公司</t>
-        </is>
-      </c>
+          <t>Halcyon Re Asia Ltd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>kbproperties.com.hk</t>
+          <t>halcyonre.com.hk</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -661,7 +657,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7 days</t>
+          <t>0 days</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -678,13 +674,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CloudDesk Inc.</t>
+          <t>Meridian Fine Art Insurance Ltd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>clouddesk.io</t>
+          <t>meridianfineart.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -709,7 +705,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>docs/contracts/S05_clouddesk_order_form.pdf</t>
+          <t>docs/contracts/S05_art_insurance_policy_2025.pdf</t>
         </is>
       </c>
     </row>
